--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/Distrito_Goo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_ECDF7407AB419C0A1EDF709B44404A2DFA167DFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F868576A-C11B-4E46-A384-FAF184A246C3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_ECDF7407AB419C0A1EDF709B44404A2DFA167DFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B19FC687-3FED-4004-9A57-E8DA4263153E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">Concurso de Venta </t>
   </si>
   <si>
-    <t xml:space="preserve">Enfoca a los dos Cursos Activos </t>
-  </si>
-  <si>
     <t>https://sbx-mx.github.io/concurso_venta/</t>
   </si>
   <si>
     <t>EVT-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enfoca a los dos Concurso Activos </t>
   </si>
 </sst>
 </file>
@@ -4390,7 +4390,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4535,11 +4535,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -20627,12 +20626,12 @@
         <v>1313</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D3" s="32">
         <v>46204</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="32">
         <v>46244</v>
       </c>
       <c r="F3" s="30" t="s">
@@ -20647,8 +20646,8 @@
       <c r="I3" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="J3" s="55" t="s">
-        <v>1315</v>
+      <c r="J3" s="54" t="s">
+        <v>1314</v>
       </c>
       <c r="K3" s="30" t="s">
         <v>439</v>
@@ -21478,7 +21477,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="30" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B28" s="52" t="s">
         <v>1301</v>
@@ -21489,7 +21488,7 @@
       <c r="D28" s="32">
         <v>46371</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="53">
         <v>46372</v>
       </c>
       <c r="F28" s="30" t="s">

--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informativo" sheetId="1" r:id="R086ef0f4413348e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WFM" sheetId="2" r:id="Re13a4f0fed6f4d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT" sheetId="3" r:id="R4dc6c38e57e7498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TBW" sheetId="4" r:id="R42444e8fd1f549f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS" sheetId="5" r:id="R5cb4b65afa7c4d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" r:id="R680465be61be4515"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="7" r:id="R69759ae2459d4e19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Semanales" sheetId="8" r:id="R391ff60c46c34d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Diaria" sheetId="9" r:id="Rd79773c0524749fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Roster" sheetId="10" r:id="R86c8047a093041f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Detail" sheetId="11" r:id="R4f176b43e1a3481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Apertura" sheetId="12" r:id="Rf6839f1217934239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identidad" sheetId="13" r:id="R9f9570778f5b451e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aniversarios_Cumpleanos" sheetId="14" r:id="Ra8bcf00136074e41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informativo" sheetId="1" r:id="R3a666201d1fe4b21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WFM" sheetId="2" r:id="R2c9b5b28083a4871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT" sheetId="3" r:id="R2ae42d685c714296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TBW" sheetId="4" r:id="Rfbe97251a6e24a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS" sheetId="5" r:id="Ra61f6d64daaf49f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" r:id="Rd0eb47d59b1d4b9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="7" r:id="R68a7d9e98bb94466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Semanales" sheetId="8" r:id="R5535166886e74ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Diaria" sheetId="9" r:id="Ra2a63a22df6a4ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Roster" sheetId="10" r:id="R87e136281e38439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Detail" sheetId="11" r:id="R468484e80b7e4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Apertura" sheetId="12" r:id="R9cd3c80c030e48ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identidad" sheetId="13" r:id="Rf8170cf2be81472c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aniversarios_Cumpleanos" sheetId="14" r:id="R8060a2f231d54c55"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4077,9 +4077,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="dd/mmm"/>
     <x:numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
   <x:fonts count="16">
     <x:font>
@@ -4410,7 +4411,7 @@
     <x:xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4566,6 +4567,7 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="4">
     <x:cellStyle name="Bueno" xfId="3"/>
@@ -5157,8 +5159,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="EventosTable" displayName="EventosTable" ref="A1:K49" totalsRowShown="0">
-  <x:autoFilter ref="A1:K49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="EventosTable" displayName="EventosTable" ref="A1:K50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:K50"/>
   <x:sortState ref="A2:K28">
     <x:sortCondition ref="D1:D28"/>
   </x:sortState>
@@ -5166,8 +5168,8 @@
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Nombre Evento"/>
     <x:tableColumn id="3" name="Descripción"/>
-    <x:tableColumn id="4" name="Fecha Inicio" dataDxfId="1"/>
-    <x:tableColumn id="5" name="Fecha Fin" dataDxfId="0"/>
+    <x:tableColumn id="4" name="Fecha Inicio"/>
+    <x:tableColumn id="5" name="Fecha Fin"/>
     <x:tableColumn id="6" name="Región"/>
     <x:tableColumn id="7" name="Distrito"/>
     <x:tableColumn id="8" name="Tienda"/>
@@ -5802,7 +5804,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24e2d6df02904318"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33cb6f58a9f045a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6007,7 +6009,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3566d227c58443f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29d50f04bcb24db7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7357,7 +7359,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d81b638c4214d3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c06ee0dac4b45a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7529,7 +7531,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5623e44ec6f445dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ca47ae8a2f4c3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17836,7 +17838,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc858b6e8519d4479"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5904365489874c09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17861,7 +17863,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f8f22263dc4641"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0284405c0b804f33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18197,7 +18199,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4df2b5f122d4367"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb225cc33ba174edf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19015,7 +19017,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bd6cad1ba4542fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21552078262b4906"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19115,7 +19117,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6155e89b0e9849e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61814a01899b4d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20658,7 +20660,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc25b93f8750a42d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32359077c1f84475"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22320,13 +22322,48 @@
         <x:v>437</x:v>
       </x:c>
     </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>EVT-049</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>ECO 2026 | Referente operativo</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Consulta el referente ECO 2026 y valida oportunamente los requerimientos aplicables. Acceso disponible en Slik Pro.</x:v>
+      </x:c>
+      <x:c r="D50" s="55" t="n">
+        <x:v>46235.5</x:v>
+      </x:c>
+      <x:c r="E50" s="55" t="n">
+        <x:v>46257.5</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>Centro Norte</x:v>
+      </x:c>
+      <x:c r="G50" t="str">
+        <x:v>Enrique Cesar Flores</x:v>
+      </x:c>
+      <x:c r="H50" t="str">
+        <x:v>Todas</x:v>
+      </x:c>
+      <x:c r="I50" t="str">
+        <x:v>VERDADERO</x:v>
+      </x:c>
+      <x:c r="J50" t="str">
+        <x:v>https://app.slikpro.com/login/alsea</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>eco_2026.jpeg</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="Rf09876480a714313"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="Rde9a6e0f22d04e44"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f4a60ca50e3436f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b9f34ce0cc4025"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22712,7 +22749,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6b143ff58ad43cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6754ecfd0add44b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23017,7 +23054,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf37ae3b5322f4bf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R537ed1f888fc4108"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informativo" sheetId="1" r:id="Rdfcf66df8a1645f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WFM" sheetId="2" r:id="R0006c4339df64480"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT" sheetId="3" r:id="R4e6b9950bf4e4f27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TBW" sheetId="4" r:id="Refe806989f7b428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS" sheetId="5" r:id="R4e8a8fdc913145ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" r:id="Rc96410c41da347d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="7" r:id="Ra507f30039b947f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Semanales" sheetId="8" r:id="Rae6589b4ffc74012"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Diaria" sheetId="9" r:id="Re18fd8d73ecc48f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Roster" sheetId="10" r:id="Re2db70cac4b84836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Detail" sheetId="11" r:id="R4783062bc8f44325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Apertura" sheetId="12" r:id="Ra10c96a16eed45a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identidad" sheetId="13" r:id="R180f8963adc74197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aniversarios_Cumpleanos" sheetId="14" r:id="Rec00dcad81634ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informativo" sheetId="1" r:id="R19175a76e4424dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WFM" sheetId="2" r:id="R9181d12a0a5c457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT" sheetId="3" r:id="Rf25d88081d2240c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TBW" sheetId="4" r:id="Rcf5c596fde2c4038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS" sheetId="5" r:id="R979586ff7f31498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" r:id="R9f5049f608514a2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="7" r:id="R4ede914d7d024cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Semanales" sheetId="8" r:id="R5e8b5685721d49ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Diaria" sheetId="9" r:id="R33c84ed54b644214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Roster" sheetId="10" r:id="R1828a27b2fcb4810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Detail" sheetId="11" r:id="Re43ae6d3f3bc40f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Apertura" sheetId="12" r:id="Rf85cca2618544d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identidad" sheetId="13" r:id="R6573927d76a946ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aniversarios_Cumpleanos" sheetId="14" r:id="R735de1734996454d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4696,8 +4696,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actividades_Diaria13" displayName="Actividades_Diaria13" ref="A1:P8" headerRowBorderDxfId="17">
-  <x:autoFilter ref="A1:P8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Actividades_Diaria13" displayName="Actividades_Diaria13" ref="A1:P9" headerRowCount="1" totalsRowCount="0" headerRowBorderDxfId="17">
+  <x:autoFilter ref="A1:P9"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Actividad"/>
@@ -5526,8 +5526,53 @@
       </x:c>
     </x:row>
     <x:row r="9">
+      <x:c r="A9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Fechas importantes en movimientos HCM</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Consulta las fechas de captura y aprobación para transferencias y ascensos en HCM.</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>movimiento_hcm.jpeg</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Mensual</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Personas</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>📅</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Azul</x:v>
+      </x:c>
+      <x:c r="J9" s="54" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>Importante</x:v>
+      </x:c>
       <x:c r="L9" s="62"/>
       <x:c r="M9" s="62"/>
+      <x:c r="N9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="Q9" t="str">
+        <x:v>Personas</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="L10" s="62"/>
@@ -9511,7 +9556,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78d48eb3f8454bab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R305e4b0876c045d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9716,7 +9761,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40741946081d4a3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2470056c95454947"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11071,7 +11116,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R006b77c608344899"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4be6ce2dfaa46ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11243,7 +11288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf888d425fa864801"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f6fed483e64236"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21353,7 +21398,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d13ea7d39924750"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42d9fc59d3d74630"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21378,7 +21423,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R529c076f1aa34559"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500a3f9bdf84461f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21454,7 +21499,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e81eba142a341e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raacd528b2add4213"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22272,7 +22317,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39a7fd8fb7d8469b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R532a4edb6a5e43b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22413,7 +22458,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R673cf1d37e1c40db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1abe55dc3edc4d4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23964,7 +24009,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3207dd74bfc44dc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15fe91bce78b4f0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29454,11 +29499,11 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="R4720840ae5214b29"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="R715a46f6f83341ea"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R047476cbc4e544f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dcb043fb1ad40b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29844,7 +29889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R358c67e44d8e4b12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e57a8d4be3b46cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30158,7 +30203,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa27eda75cbe4b6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f7b33c67237454e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informativo" sheetId="1" r:id="R19175a76e4424dba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WFM" sheetId="2" r:id="R9181d12a0a5c457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT" sheetId="3" r:id="Rf25d88081d2240c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TBW" sheetId="4" r:id="Rcf5c596fde2c4038"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS" sheetId="5" r:id="R979586ff7f31498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" r:id="R9f5049f608514a2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="7" r:id="R4ede914d7d024cfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Semanales" sheetId="8" r:id="R5e8b5685721d49ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Diaria" sheetId="9" r:id="R33c84ed54b644214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Roster" sheetId="10" r:id="R1828a27b2fcb4810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Detail" sheetId="11" r:id="Re43ae6d3f3bc40f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Apertura" sheetId="12" r:id="Rf85cca2618544d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identidad" sheetId="13" r:id="R6573927d76a946ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aniversarios_Cumpleanos" sheetId="14" r:id="R735de1734996454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informativo" sheetId="1" r:id="R10c23a5a459f4e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WFM" sheetId="2" r:id="Rf7de9a47275a4d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT" sheetId="3" r:id="R50234bbe81e44225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TBW" sheetId="4" r:id="Rd076a5888f25497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS" sheetId="5" r:id="R475c4ff6ebca4c7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" r:id="Rcf7b980f64bb430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos" sheetId="7" r:id="Rb5228aa56b0f4a39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Semanales" sheetId="8" r:id="Rfdd337f7da654eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades_Diaria" sheetId="9" r:id="R392d38c7204f45f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Roster" sheetId="10" r:id="R629e16bda2af4cfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duty_Detail" sheetId="11" r:id="R76be03e92b3c4541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Apertura" sheetId="12" r:id="R47928ef0fb7648f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identidad" sheetId="13" r:id="R05233f6e86804544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aniversarios_Cumpleanos" sheetId="14" r:id="Re6e9a171103047f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4309,7 +4309,7 @@
     <x:xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="66">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4493,6 +4493,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="14" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="4">
@@ -4886,7 +4889,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="EventosTable" displayName="EventosTable" ref="A1:L45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="EventosTable" displayName="EventosTable" ref="A1:L48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Nombre Evento"/>
@@ -9556,7 +9559,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R305e4b0876c045d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7d7ead461b94e5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2470056c95454947"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d2859cbe54f4a06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11116,7 +11119,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4be6ce2dfaa46ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75759e7a7f964b7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11288,7 +11291,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f6fed483e64236"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R483bed295e77427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21398,7 +21401,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42d9fc59d3d74630"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe31f366f55a41ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21423,7 +21426,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500a3f9bdf84461f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra333ae80b9d249b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21499,7 +21502,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raacd528b2add4213"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R941d64ad34124a60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22317,7 +22320,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R532a4edb6a5e43b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rede8b13068844c69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22458,7 +22461,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1abe55dc3edc4d4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Race01e56bbc94af4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24009,7 +24012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15fe91bce78b4f0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c0badb32bf4705"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25669,17 +25672,119 @@
         <x:v>Informativo</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="D46" s="62"/>
-      <x:c r="E46" s="62"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="D47" s="62"/>
-      <x:c r="E47" s="62"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="D48" s="62"/>
-      <x:c r="E48" s="62"/>
+    <x:row r="46" ht="30" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>EVT-045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Unicorn Frappuccino · Mecánica del concurso</x:v>
+      </x:c>
+      <x:c r="C46" s="65" t="str">
+        <x:v>Evento importante. Consulta la mecánica, metas y premios; prepara del 8 al 18 de agosto y ejecuta la dinámica principal del 15 al 17.</x:v>
+      </x:c>
+      <x:c r="D46" s="62" t="n">
+        <x:v>46242.5</x:v>
+      </x:c>
+      <x:c r="E46" s="62" t="n">
+        <x:v>46252.5</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Centro Norte</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Enrique Cesar Flores</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Todas</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>VERDADERO</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>concurso_unicorn.jpg</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>🦄</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>Imagen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="30" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>EVT-046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Unicorn Frappuccino · Checklist operativo</x:v>
+      </x:c>
+      <x:c r="C47" s="65" t="str">
+        <x:v>Evento importante. Valida staffing, stocking, estándares, layout y seguimiento comercial antes y durante la ejecución del 15 al 17 de agosto.</x:v>
+      </x:c>
+      <x:c r="D47" s="62" t="n">
+        <x:v>46242.5</x:v>
+      </x:c>
+      <x:c r="E47" s="62" t="n">
+        <x:v>46252.5</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>Centro Norte</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>Enrique Cesar Flores</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Todas</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>VERDADERO</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>checklisunicorn.png</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>✅</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>Imagen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="30" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>EVT-047</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Unicorn Frappuccino · Mejores prácticas</x:v>
+      </x:c>
+      <x:c r="C48" s="65" t="str">
+        <x:v>Evento importante. Revisa receta, insumos, smallwares, salsa azul y venta sugerida para una ejecución consistente y segura.</x:v>
+      </x:c>
+      <x:c r="D48" s="62" t="n">
+        <x:v>46242.5</x:v>
+      </x:c>
+      <x:c r="E48" s="62" t="n">
+        <x:v>46252.5</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>Centro Norte</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>Enrique Cesar Flores</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>Todas</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>VERDADERO</x:v>
+      </x:c>
+      <x:c r="J48" t="str">
+        <x:v>best_practice_unicorn.jpg</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>⭐</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>Imagen</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="D49" s="62"/>
@@ -29499,11 +29604,11 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="R715a46f6f83341ea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="Rdd45966bb4ea4f6b"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dcb043fb1ad40b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5897d8ba27f64f08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29889,7 +29994,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e57a8d4be3b46cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf78c88382190428f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30203,7 +30308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f7b33c67237454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62ef6f6d84444794"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F733625D-6E7E-4C42-BECE-2B581390181B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F4D4EC-3252-4149-A7FF-32D9C732A7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="1335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4405" uniqueCount="1338">
   <si>
     <t>ID</t>
   </si>
@@ -4052,13 +4052,22 @@
     <t>https://sbx-mx.github.io/Manual_Recetario/</t>
   </si>
   <si>
-    <t>Evalua Estandares Operativos</t>
-  </si>
-  <si>
     <t>Esfuerzo Operativo</t>
   </si>
   <si>
     <t>Venta Sugestiva Donas + Cake Pop + Galleta  | Merch</t>
+  </si>
+  <si>
+    <t>https://sbx-mx.github.io/Esfuerzo_Operativo/</t>
+  </si>
+  <si>
+    <t>Evalua Estandares Operativos, Recetas , Practica y Mejora</t>
+  </si>
+  <si>
+    <t>Practica la Bebida, Conoce los Objetivos</t>
+  </si>
+  <si>
+    <t>Unicorn Frapp PREPAREMONOS MÁS</t>
   </si>
 </sst>
 </file>
@@ -4998,7 +5007,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="EventosTable" displayName="EventosTable" ref="A1:L48" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="EventosTable" displayName="EventosTable" ref="A1:L49" totalsRowShown="0">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Nombre Evento"/>
@@ -22700,7 +22709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="29">
+    <row r="4" spans="1:12">
       <c r="A4" s="36" t="s">
         <v>21</v>
       </c>
@@ -22828,7 +22837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="29">
+    <row r="8" spans="1:12">
       <c r="A8" s="36" t="s">
         <v>21</v>
       </c>
@@ -24134,7 +24143,7 @@
       <c r="H48" s="40"/>
       <c r="I48" s="40"/>
       <c r="J48" s="40" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="K48" s="40" t="s">
         <v>27</v>
@@ -24154,19 +24163,19 @@
         <v>345</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E49" s="40" t="s">
         <v>170</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="G49" s="40"/>
       <c r="H49" s="40"/>
       <c r="I49" s="40"/>
       <c r="J49" s="40" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="K49" s="37" t="s">
         <v>26</v>
@@ -24176,7 +24185,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" sqref="E2:E999" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"web,app"</formula1>
     </dataValidation>
@@ -25942,67 +25951,101 @@
         <v>359</v>
       </c>
     </row>
-    <row r="49" spans="4:5">
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-    </row>
-    <row r="50" spans="4:5">
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D49" s="57">
+        <v>46242.5</v>
+      </c>
+      <c r="E49" s="57">
+        <v>46252.5</v>
+      </c>
+      <c r="F49" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" t="s">
+        <v>96</v>
+      </c>
+      <c r="H49" t="s">
+        <v>363</v>
+      </c>
+      <c r="I49" t="s">
+        <v>364</v>
+      </c>
+      <c r="J49" t="s">
+        <v>1331</v>
+      </c>
+      <c r="K49" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L49" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="D50" s="57"/>
       <c r="E50" s="57"/>
     </row>
-    <row r="51" spans="4:5">
+    <row r="51" spans="1:12">
       <c r="D51" s="57"/>
       <c r="E51" s="57"/>
     </row>
-    <row r="52" spans="4:5">
+    <row r="52" spans="1:12">
       <c r="D52" s="57"/>
       <c r="E52" s="57"/>
     </row>
-    <row r="53" spans="4:5">
+    <row r="53" spans="1:12">
       <c r="D53" s="57"/>
       <c r="E53" s="57"/>
     </row>
-    <row r="54" spans="4:5">
+    <row r="54" spans="1:12">
       <c r="D54" s="57"/>
       <c r="E54" s="57"/>
     </row>
-    <row r="55" spans="4:5">
+    <row r="55" spans="1:12">
       <c r="D55" s="57"/>
       <c r="E55" s="57"/>
     </row>
-    <row r="56" spans="4:5">
+    <row r="56" spans="1:12">
       <c r="D56" s="57"/>
       <c r="E56" s="57"/>
     </row>
-    <row r="57" spans="4:5">
+    <row r="57" spans="1:12">
       <c r="D57" s="57"/>
       <c r="E57" s="57"/>
     </row>
-    <row r="58" spans="4:5">
+    <row r="58" spans="1:12">
       <c r="D58" s="57"/>
       <c r="E58" s="57"/>
     </row>
-    <row r="59" spans="4:5">
+    <row r="59" spans="1:12">
       <c r="D59" s="57"/>
       <c r="E59" s="57"/>
     </row>
-    <row r="60" spans="4:5">
+    <row r="60" spans="1:12">
       <c r="D60" s="57"/>
       <c r="E60" s="57"/>
     </row>
-    <row r="61" spans="4:5">
+    <row r="61" spans="1:12">
       <c r="D61" s="57"/>
       <c r="E61" s="57"/>
     </row>
-    <row r="62" spans="4:5">
+    <row r="62" spans="1:12">
       <c r="D62" s="57"/>
       <c r="E62" s="57"/>
     </row>
-    <row r="63" spans="4:5">
+    <row r="63" spans="1:12">
       <c r="D63" s="57"/>
       <c r="E63" s="57"/>
     </row>
-    <row r="64" spans="4:5">
+    <row r="64" spans="1:12">
       <c r="D64" s="57"/>
       <c r="E64" s="57"/>
     </row>

--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F5CB48-C91E-4D2A-ABF6-2FB38E4F5316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F385A3F4-AF65-44BE-B4C9-06BE1B3CF185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Distrito_Go_CMS_v2_actualizado.xlsx
+++ b/Distrito_Go_CMS_v2_actualizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90017073-903B-447A-87CD-1E60BD1D592F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EACF52-561B-4679-AEA1-9D3B25C839BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4718" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4726" uniqueCount="1350">
   <si>
     <t>ID</t>
   </si>
@@ -4095,6 +4095,15 @@
   </si>
   <si>
     <t>Bienvenida a Pumpkin</t>
+  </si>
+  <si>
+    <t>🏛️</t>
+  </si>
+  <si>
+    <t>LayOut 2.0</t>
+  </si>
+  <si>
+    <t>https://sbx-mex.github.io/Lay-Out_2.0/</t>
   </si>
 </sst>
 </file>
@@ -4134,7 +4143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -4205,11 +4214,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9D8D1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4238,11 +4256,47 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF12372A"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFC9D8D1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFC9D8D1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF8B3A2A"/>
@@ -4661,15 +4715,18 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="CmsLinks" displayName="CmsLinks" ref="A1:L49" totalsRowShown="0">
-  <autoFilter ref="A1:L49" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="CmsLinks" displayName="CmsLinks" ref="A1:L50" totalsRowShown="0">
+  <autoFilter ref="A1:L50" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L50">
+    <sortCondition ref="L1:L50"/>
+  </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Categoria"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Grupo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Icono"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Nombre"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Tipo"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="URL"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="URL" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="WebURL"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Package"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="PlayStore"/>
@@ -5523,21 +5580,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:V10">
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="19" priority="7">
       <formula>$A2=90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J10">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O10">
-    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="No"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P10">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="whole" sqref="F2:F10" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -7124,8 +7181,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G58">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" sqref="C2:C58" xr:uid="{00000000-0002-0000-0A00-000000000000}">
@@ -7561,8 +7618,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="G2:G9" xr:uid="{00000000-0002-0000-0C00-000000000000}">
@@ -17428,8 +17485,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I281">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="I2:I281" xr:uid="{00000000-0002-0000-0D00-000000000000}">
@@ -18520,7 +18577,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -18611,16 +18668,16 @@
         <v>183</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>188</v>
+        <v>1347</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>189</v>
+        <v>1348</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>190</v>
+        <v>1349</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -20113,23 +20170,58 @@
         <v>48</v>
       </c>
     </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L50" s="11">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K49">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="No"/>
+  <conditionalFormatting sqref="K2:K50">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="K2:K49" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" sqref="K2:K50" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="L2:L49" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="whole" sqref="L2:L50" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>0</formula1>
       <formula2>999</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{765FD9A2-CFEF-49CE-96FA-09F123020226}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21942,8 +22034,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I49">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" sqref="I2:I49" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -22655,8 +22747,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J8">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Sí"/>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="No"/>
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Sí"/>
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="No"/>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="whole" sqref="F2:F8" xr:uid="{00000000-0002-0000-0800-000000000000}">
